--- a/2025/CBD/Practica/Practica 5/ejercicios.xlsx
+++ b/2025/CBD/Practica/Practica 5/ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\2025\CBD\Practica\Practica 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6354FE1A-5071-4D02-B94D-9E2E4EC638FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2A9CFD-1051-40DC-9681-C8390DD6798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{309868A5-3B58-401D-9D8B-158D56E3611E}"/>
   </bookViews>
@@ -246,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -254,9 +254,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -598,7 +595,7 @@
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="54" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -710,13 +707,13 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B8" t="s">
@@ -808,7 +805,7 @@
       <c r="E12">
         <v>3</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="1">
         <v>3</v>
       </c>
       <c r="G12" t="s">
@@ -862,12 +859,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B19" t="s">
@@ -890,7 +887,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B20" t="s">
@@ -910,7 +907,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>-33691</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -933,7 +930,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>-1981</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -962,7 +959,7 @@
       <c r="E23">
         <v>3</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="1">
         <v>3</v>
       </c>
       <c r="G23" t="s">
@@ -1028,12 +1025,12 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>-16533</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
@@ -1056,7 +1053,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
@@ -1119,7 +1116,7 @@
       <c r="E34">
         <v>3</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="1">
         <v>3</v>
       </c>
       <c r="G34" t="s">
@@ -1519,9 +1516,6 @@
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1596,6 +1590,9 @@
         <v>3</v>
       </c>
       <c r="G25" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1669,9 +1666,6 @@
       <c r="F32">
         <v>3</v>
       </c>
-      <c r="G32" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
@@ -1742,6 +1736,9 @@
       </c>
       <c r="G36" t="s">
         <v>54</v>
+      </c>
+      <c r="H36" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
